--- a/data/trans_camb/P19C08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,23</t>
+          <t>-0,55; 1,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,29; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,97</t>
+          <t>-0,26; 4,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,31</t>
+          <t>-0,21; 2,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,0</t>
+          <t>-1,32; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,14</t>
+          <t>-0,26; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,37</t>
+          <t>-0,12; 1,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,0</t>
+          <t>-0,92; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,73</t>
+          <t>-0,01; 2,99</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,92; —</t>
+          <t>-95,74; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,46</t>
+          <t>-0,53; 1,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,16</t>
+          <t>-1,33; -0,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; -0,09</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,29</t>
+          <t>-0,86; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,15</t>
+          <t>-1,9; -0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,28</t>
+          <t>-1,6; 0,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,04</t>
+          <t>-0,4; 1,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,23</t>
+          <t>-1,29; -0,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; -0,01</t>
+          <t>-1,11; -0,01</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,1; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 395,18</t>
+          <t>-52,5; 441,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,8</t>
+          <t>-100,0; 323,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,52</t>
+          <t>-0,73; 0,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,38</t>
+          <t>-0,88; 0,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,21</t>
+          <t>-0,5; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,44</t>
+          <t>-0,26; 1,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,99</t>
+          <t>-0,62; 1,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,02</t>
+          <t>-0,41; 1,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,85</t>
+          <t>-0,29; 0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,45</t>
+          <t>-0,53; 0,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,96</t>
+          <t>-0,26; 0,89</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,21; —</t>
+          <t>-73,81; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,51; —</t>
+          <t>-84,26; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 666,84</t>
+          <t>-59,68; 678,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 518,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 837,93</t>
+          <t>-52,71; 694,16</t>
         </is>
       </c>
     </row>
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,93</t>
+          <t>-0,61; 1,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,0</t>
+          <t>-1,35; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,11</t>
+          <t>-1,41; 0,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,36</t>
+          <t>-0,6; 1,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,57; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,45</t>
+          <t>-1,13; 0,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,29</t>
+          <t>-0,35; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; -0,11</t>
+          <t>-1,13; -0,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 878,44</t>
+          <t>-71,7; 797,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-93,43; 144,49</t>
+          <t>-93,14; 158,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,45</t>
+          <t>0,15; 1,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,25</t>
+          <t>-1,88; 0,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,19</t>
+          <t>-1,87; 0,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,14</t>
+          <t>-1,0; 0,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,7</t>
+          <t>-0,58; 0,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,47</t>
+          <t>-0,77; 0,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,78</t>
+          <t>-1,41; 0,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,8</t>
+          <t>-1,4; 0,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,7</t>
+          <t>-1,93; 0,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,31</t>
+          <t>-2,47; 0,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,15</t>
+          <t>-1,26; 0,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,16</t>
+          <t>-1,47; 0,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,33</t>
+          <t>-1,28; 0,31</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-93,95; 224,77</t>
+          <t>-92,69; 262,49</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,03</t>
+          <t>0,44; 4,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,37 +1983,37 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,0</t>
+          <t>-3,71; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,05</t>
+          <t>-2,27; 2,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,26</t>
+          <t>-3,66; 0,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,88</t>
+          <t>-1,48; 0,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,22</t>
+          <t>-1,45; 1,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,34</t>
+          <t>-2,0; 0,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,76</t>
+          <t>-0,1; 0,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,08</t>
+          <t>-0,48; 0,07</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,5</t>
+          <t>-0,2; 0,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,47</t>
+          <t>-0,33; 0,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; -0,02</t>
+          <t>-0,7; 0,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,16</t>
+          <t>-0,55; 0,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,45</t>
+          <t>-0,13; 0,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,48; -0,05</t>
+          <t>-0,52; -0,05</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,21</t>
+          <t>-0,28; 0,21</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 394,86</t>
+          <t>-26,28; 324,15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-92,62; 58,92</t>
+          <t>-87,75; 71,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 280,4</t>
+          <t>-45,72; 263,85</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 130,68</t>
+          <t>-44,4; 144,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 5,38</t>
+          <t>-89,02; 18,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 49,69</t>
+          <t>-67,82; 47,09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 137,44</t>
+          <t>-23,38; 149,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-83,67; -10,35</t>
+          <t>-84,12; -5,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 65,62</t>
+          <t>-48,33; 64,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,0</t>
+          <t>-0,55; 1,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>-1,32; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,43</t>
+          <t>-0,26; 4,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,29</t>
+          <t>-0,05; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-1,31; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,71</t>
+          <t>-0,4; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,43</t>
+          <t>-0,13; 1,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,0</t>
+          <t>-0,93; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,99</t>
+          <t>-0,04; 2,4</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>366,01%</t>
+          <t>334,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>262,11%</t>
+          <t>235,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>320,54%</t>
+          <t>287,66%</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-95,74; —</t>
+          <t>-67,66; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,61</t>
+          <t>-0,51; 1,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,16</t>
+          <t>-1,34; -0,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,0</t>
+          <t>-0,82; 2,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,28</t>
+          <t>-0,94; 1,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; -0,15</t>
+          <t>-1,87; -0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,23</t>
+          <t>-1,44; 0,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,06</t>
+          <t>-0,43; 0,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; -0,24</t>
+          <t>-1,21; -0,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; -0,01</t>
+          <t>-0,82; 0,85</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-91,79%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-67,57%</t>
+          <t>-65,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-76,46%</t>
+          <t>-30,89%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,1; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 441,45</t>
+          <t>-58,3; 394,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,06</t>
+          <t>-100,0; 622,8</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,66</t>
+          <t>-0,72; 0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,37</t>
+          <t>-0,85; 0,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,41</t>
+          <t>-0,47; 1,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,32</t>
+          <t>-0,38; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,07</t>
+          <t>-0,59; 0,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,09</t>
+          <t>-0,45; 1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,79</t>
+          <t>-0,3; 0,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,56</t>
+          <t>-0,52; 0,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,89</t>
+          <t>-0,25; 0,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>105,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,81; —</t>
+          <t>-85,37; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,26; —</t>
+          <t>-79,5; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 678,09</t>
+          <t>-60,97; 668,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 363,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 694,16</t>
+          <t>-54,04; 551,5</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,99</t>
+          <t>-0,49; 2,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,0</t>
+          <t>-1,59; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,14</t>
+          <t>-1,35; 0,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,57</t>
+          <t>-0,7; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,4</t>
+          <t>-1,05; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,26</t>
+          <t>-0,37; 1,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; -0,12</t>
+          <t>-1,14; -0,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,15</t>
+          <t>-0,86; 0,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-75,27%</t>
+          <t>-63,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,75%</t>
+          <t>-22,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,62%</t>
+          <t>-42,09%</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,7; 797,48</t>
+          <t>-65,89; 713,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-93,14; 158,37</t>
+          <t>-90,32; 232,39</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,53</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,33</t>
+          <t>-1,61; 0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,17</t>
+          <t>-1,8; 0,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,22</t>
+          <t>-0,87; 0,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,73</t>
+          <t>-0,68; 0,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,44</t>
+          <t>-0,61; 0,55</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-72,22%</t>
+          <t>-45,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,81; —</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,78</t>
+          <t>-1,71; 0,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,8</t>
+          <t>-1,45; 0,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,64</t>
+          <t>-1,43; 0,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,61; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,61; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,3</t>
+          <t>-2,09; 0,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,15</t>
+          <t>-1,47; 0,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,15</t>
+          <t>-1,46; 0,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,31</t>
+          <t>-1,27; 0,47</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-0,07%</t>
+          <t>-1,72%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-62,88%</t>
+          <t>-43,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-43,84%</t>
+          <t>-29,26%</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-92,69; 262,49</t>
+          <t>-90,92; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,33</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,37</t>
+          <t>0,43; 3,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,37 +1983,37 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,0</t>
+          <t>-3,92; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,02</t>
+          <t>-2,77; 1,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,26</t>
+          <t>-3,22; 0,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,99</t>
+          <t>-1,52; 0,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,18</t>
+          <t>-1,47; 1,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,36</t>
+          <t>-1,7; 0,41</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-76,83%</t>
+          <t>-76,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-49,41%</t>
+          <t>-47,66%</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,68</t>
+          <t>-0,06; 0,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,07</t>
+          <t>-0,49; 0,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,52</t>
+          <t>-0,16; 0,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,48</t>
+          <t>-0,29; 0,46</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,01</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,14</t>
+          <t>-0,47; 0,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,46</t>
+          <t>-0,11; 0,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,52; -0,05</t>
+          <t>-0,5; -0,05</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,21</t>
+          <t>-0,2; 0,31</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-30,04%</t>
+          <t>-17,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-7,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 324,15</t>
+          <t>-22,48; 342,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 71,2</t>
+          <t>-91,41; 50,28</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 263,85</t>
+          <t>-36,82; 292,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 144,62</t>
+          <t>-42,55; 144,21</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-89,02; 18,05</t>
+          <t>-89,73; 17,98</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 47,09</t>
+          <t>-60,28; 71,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 149,22</t>
+          <t>-20,08; 149,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -5,29</t>
+          <t>-85,2; -15,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 64,82</t>
+          <t>-36,57; 104,59</t>
         </is>
       </c>
     </row>
